--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$186</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6033" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6066" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1871,6 +1871,21 @@
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>Type de diplôme, par exemple : DE, DES, CES, etc.</t>
+  </si>
+  <si>
+    <t>typeDiplome</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.text</t>
@@ -2228,7 +2243,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ185"/>
+  <dimension ref="A1:AJ186"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.60546875" customWidth="true" bestFit="true"/>
@@ -9039,7 +9054,7 @@
         <v>90</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -20887,9 +20902,11 @@
         <v>600</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C182" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="D182" t="s" s="2">
         <v>71</v>
       </c>
@@ -20898,10 +20915,10 @@
         <v>72</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>71</v>
@@ -20910,19 +20927,19 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>230</v>
+        <v>602</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>232</v>
+        <v>603</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>71</v>
@@ -20947,13 +20964,11 @@
         <v>71</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>71</v>
+        <v>604</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>71</v>
@@ -20971,13 +20986,13 @@
         <v>71</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>90</v>
@@ -20988,10 +21003,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21002,7 +21017,7 @@
         <v>72</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>71</v>
@@ -21011,22 +21026,22 @@
         <v>71</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>249</v>
+        <v>163</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>602</v>
+        <v>230</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>603</v>
+        <v>231</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>604</v>
+        <v>233</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>71</v>
@@ -21075,7 +21090,7 @@
         <v>71</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>601</v>
+        <v>234</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>72</v>
@@ -21087,15 +21102,15 @@
         <v>90</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>254</v>
+        <v>91</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21118,18 +21133,20 @@
         <v>71</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O184" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>71</v>
       </c>
@@ -21177,7 +21194,7 @@
         <v>71</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>72</v>
@@ -21189,15 +21206,15 @@
         <v>90</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21211,7 +21228,7 @@
         <v>72</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>71</v>
@@ -21220,7 +21237,7 @@
         <v>71</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>610</v>
+        <v>256</v>
       </c>
       <c r="L185" t="s" s="2">
         <v>611</v>
@@ -21231,9 +21248,7 @@
       <c r="N185" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="O185" t="s" s="2">
-        <v>614</v>
-      </c>
+      <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>71</v>
       </c>
@@ -21257,11 +21272,13 @@
         <v>71</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y185" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="Y185" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="Z185" t="s" s="2">
-        <v>615</v>
+        <v>71</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>71</v>
@@ -21279,23 +21296,125 @@
         <v>71</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ185" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="186" hidden="true">
+      <c r="A186" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G186" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="P186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q186" s="2"/>
+      <c r="R186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="Y186" s="2"/>
+      <c r="Z186" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
         <v>91</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ185">
+  <autoFilter ref="A1:AJ186">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21305,7 +21424,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI184">
+  <conditionalFormatting sqref="A2:AI185">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
